--- a/output.xlsx
+++ b/output.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hossein\Github\Wolfe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E962C2-25D8-460E-BC17-EC730BA71717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EE69D0-ED47-4171-8E5C-9C35B95C7345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="16">
   <si>
     <t>n</t>
   </si>
@@ -71,12 +71,15 @@
   <si>
     <t>0.000000292416495‬</t>
   </si>
+  <si>
+    <t>0.0016884692795764‬</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,13 +87,60 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -105,9 +155,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -388,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="17.59765625" customWidth="1"/>
@@ -399,43 +456,43 @@
     <col min="11" max="11" width="13.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B2">
@@ -469,8 +526,8 @@
         <v>7.2722720000000004E-9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B3">
@@ -504,40 +561,41 @@
         <v>7.2722720000000004E-9</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1">
+      <c r="B4" s="3"/>
+      <c r="C4" s="4">
         <v>-3.1493631455282898E-7</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B5">
@@ -572,8 +630,8 @@
         <v>2.5935790000000003E-10</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B6">
@@ -607,40 +665,41 @@
         <v>2.5935790000000003E-10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="1">
+      <c r="B7" s="3"/>
+      <c r="C7" s="4">
         <v>-1.8905045831838298E-8</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B8">
@@ -674,8 +733,8 @@
         <v>2.4687669999999998E-9</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B9">
@@ -709,40 +768,41 @@
         <v>2.4687669999999998E-9</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="1">
+      <c r="B10" s="3"/>
+      <c r="C10" s="4">
         <v>-1.99500182885099E-8</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B11">
@@ -777,8 +837,8 @@
         <v>9.1429229999999996E-10</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B12">
@@ -812,37 +872,41 @@
         <v>9.1429220000000003E-10</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C13" s="1">
+    <row r="13" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="4">
         <v>-1.46352231144198E-8</v>
       </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B14">
@@ -876,8 +940,8 @@
         <v>3.7443890000000002E-9</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B15">
@@ -911,37 +975,41 @@
         <v>3.7443869999999996E-9</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C16" s="1">
+    <row r="16" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="4">
         <v>-7.9300112465619899E-8</v>
       </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B17">
@@ -975,8 +1043,8 @@
         <v>6.0399299999999998E-9</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B18">
@@ -1010,37 +1078,41 @@
         <v>6.0399299999999998E-9</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C19" s="1">
+    <row r="19" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4">
         <v>-4.7288566278725702E-8</v>
       </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
+      <c r="D19" s="3">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
         <v>2.0772524679999999E-7</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B20">
@@ -1074,8 +1146,8 @@
         <v>5.7075869999999996E-9</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B21">
@@ -1109,37 +1181,41 @@
         <v>5.7071370000000001E-9</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C22" s="1">
+    <row r="22" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4">
         <v>-1.71197345512277E-7</v>
       </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B23">
@@ -1173,8 +1249,8 @@
         <v>6.5554329999999997E-9</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B24">
@@ -1208,37 +1284,41 @@
         <v>6.5495689999999998E-9</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C25" s="1">
+    <row r="25" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="4">
         <v>-1.9880471249035201E-7</v>
       </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3">
         <v>1.1758887528999999E-6</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
-      <c r="J25">
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3">
         <v>7.2759999999999993E-12</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="3">
         <v>5.8640000000000001E-12</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="26" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B26">
@@ -1272,8 +1352,8 @@
         <v>5.704796E-9</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="27" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B27">
@@ -1307,37 +1387,41 @@
         <v>5.707705E-9</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C28" s="1">
+    <row r="28" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="4">
         <v>-1.20573527234862E-8</v>
       </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
+      <c r="D28" s="3">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3">
         <v>1.11637504751E-5</v>
       </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="I28" s="1">
-        <v>0</v>
-      </c>
-      <c r="J28" s="1">
-        <v>0</v>
-      </c>
-      <c r="K28">
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
         <v>2.9089999999999998E-12</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="29" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B29">
@@ -1371,8 +1455,8 @@
         <v>5.942536E-9</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="30" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B30">
@@ -1388,7 +1472,7 @@
         <v>3</v>
       </c>
       <c r="F30" s="1">
-        <v>-147173.5</v>
+        <v>2.2838000000000001E-2</v>
       </c>
       <c r="G30">
         <v>80</v>
@@ -1406,8 +1490,41 @@
         <v>6.3844360000000003E-9</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="31" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="4">
+        <v>-6.7631816222872593E-8</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3">
+        <v>6.6462307379409999E-4</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>1.4551920000000001E-10</v>
+      </c>
+      <c r="K31" s="3">
+        <v>4.4189999999999999E-10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B32">
@@ -1441,8 +1558,8 @@
         <v>9.1323690000000005E-9</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="33" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B33">
@@ -1476,8 +1593,41 @@
         <v>8.2320759999999999E-9</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="34" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="4">
+        <v>-7.5349595687096103E-8</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3">
+        <v>2.328306E-10</v>
+      </c>
+      <c r="K34" s="3">
+        <v>9.0029300000000003E-10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B35">
@@ -1511,8 +1661,8 @@
         <v>4.5062869999999996E-9</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="36" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B36">
@@ -1546,8 +1696,41 @@
         <v>6.5088670000000004E-9</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="37" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="4">
+        <v>-2.76583194835698E-7</v>
+      </c>
+      <c r="D37" s="3">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3">
+        <v>4.2368672472010001E-4</v>
+      </c>
+      <c r="G37" s="3">
+        <v>8</v>
+      </c>
+      <c r="H37" s="4">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3">
+        <v>5.2386899999999996E-10</v>
+      </c>
+      <c r="K37" s="3">
+        <v>2.0025799999999999E-9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B38">
@@ -1581,8 +1764,8 @@
         <v>7.1950539999999999E-9</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="39" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B39">
@@ -1616,8 +1799,41 @@
         <v>8.9768350000000003E-9</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="40" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="4">
+        <v>-4.0764117001913101E-7</v>
+      </c>
+      <c r="D40" s="3">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3">
+        <v>2.2185105958071999E-3</v>
+      </c>
+      <c r="G40" s="3">
+        <v>2</v>
+      </c>
+      <c r="H40" s="4">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3">
+        <v>1.7462297E-9</v>
+      </c>
+      <c r="K40" s="3">
+        <v>1.7817809999999999E-9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B41">
@@ -1651,8 +1867,8 @@
         <v>7.5152450000000001E-9</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="42" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B42">
@@ -1686,8 +1902,41 @@
         <v>9.5629730000000007E-9</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="43" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="4">
+        <v>-4.5890560670961098E-7</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>7.9314866176499998E-5</v>
+      </c>
+      <c r="G43" s="3">
+        <v>6</v>
+      </c>
+      <c r="H43" s="4">
+        <v>0</v>
+      </c>
+      <c r="I43" s="4">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1.862645E-9</v>
+      </c>
+      <c r="K43" s="3">
+        <v>2.0477280000000001E-9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B44">
@@ -1721,8 +1970,8 @@
         <v>8.0163349999999997E-9</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="45" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B45">
@@ -1756,15 +2005,41 @@
         <v>4.6326170000000004E-9</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>12</v>
-      </c>
+    <row r="46" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" s="3"/>
+      <c r="C46" s="4">
+        <v>-7.1655477115025498E-8</v>
+      </c>
+      <c r="D46" s="3">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3">
+        <v>5.8993639158559999E-4</v>
+      </c>
+      <c r="G46" s="3">
+        <v>5</v>
+      </c>
+      <c r="H46" s="4">
+        <v>0</v>
+      </c>
+      <c r="I46" s="4">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3">
+        <v>9.3132270000000008E-10</v>
+      </c>
+      <c r="K46" s="3">
+        <v>3.3837180000000002E-9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/output.xlsx
+++ b/output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hossein\Github\Wolfe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EE69D0-ED47-4171-8E5C-9C35B95C7345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF236157-AC7F-4EF2-B1E9-9170E636E65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17244" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,6 +122,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -155,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -165,6 +172,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -456,38 +464,38 @@
     <col min="11" max="11" width="13.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="9" t="s">
         <v>9</v>
       </c>
     </row>
